--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_288_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_288_R29.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5085</v>
+        <v>7.422</v>
       </c>
       <c r="E2" t="n">
-        <v>8.697800000000001</v>
+        <v>8.6112</v>
       </c>
       <c r="F2" t="n">
         <v>-1.1892</v>
@@ -610,10 +610,10 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4208</v>
+        <v>-0.5074</v>
       </c>
       <c r="T2" t="n">
-        <v>0.13</v>
+        <v>0.0435</v>
       </c>
       <c r="U2" t="n">
         <v>-0.5508999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9234</v>
+        <v>4.3258</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8491</v>
+        <v>3.3523</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0742</v>
+        <v>0.9734</v>
       </c>
       <c r="G3" t="n">
         <v>2.27</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2744</v>
+        <v>-0.872</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0297</v>
+        <v>-0.5265</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2447</v>
+        <v>-0.3455</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0241</v>
+        <v>2.4135</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8631</v>
+        <v>0.1773</v>
       </c>
       <c r="F4" t="n">
-        <v>1.161</v>
+        <v>2.2361</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4275</v>
+        <v>0.8312</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3936</v>
+        <v>1.3733</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0339</v>
+        <v>-0.542</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4572</v>
+        <v>0.3631</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0487</v>
+        <v>1.1126</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4085</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0297</v>
+        <v>0.4681</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6551</v>
+        <v>0.2606</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3746</v>
+        <v>0.2075</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.0461</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.955</v>
+        <v>-0.0982</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8685</v>
+        <v>0.1443</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4665</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7765</v>
+        <v>1.4273</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09</v>
+        <v>1.1737</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8664</v>
+        <v>0.2536</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8312</v>
+        <v>3.4275</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3733</v>
+        <v>2.3936</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.542</v>
+        <v>1.0339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3631</v>
+        <v>4.4572</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1126</v>
+        <v>3.0487</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.4085</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4681</v>
+        <v>-1.0297</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2606</v>
+        <v>-0.6551</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2075</v>
+        <v>-0.3746</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5909</v>
+        <v>-0.6833</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3655</v>
+        <v>-0.6445</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2254</v>
+        <v>-0.0389</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>1.4665</v>
       </c>
       <c r="W5" t="n">
         <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1593</v>
+        <v>0.2425</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7055</v>
+        <v>-1.4381</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5462</v>
+        <v>1.6806</v>
       </c>
       <c r="G7" t="n">
         <v>0.0606</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.078</v>
+        <v>-0.6763</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9709</v>
+        <v>-0.7035</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1072</v>
+        <v>0.0272</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6976</v>
+        <v>-1.9253</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2261</v>
+        <v>-3.1515</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5286</v>
+        <v>1.2261</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6963</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4626</v>
+        <v>0.2348</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2987</v>
+        <v>-0.224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7613</v>
+        <v>0.4589</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7527</v>
+        <v>-1.9311</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3644</v>
+        <v>2.0853</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1172</v>
+        <v>-4.0164</v>
       </c>
       <c r="G9" t="n">
         <v>2.5412</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.098</v>
+        <v>-0.2763</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5034</v>
+        <v>0.2243</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6014</v>
+        <v>-0.5006</v>
       </c>
       <c r="V9" t="n">
         <v>-3.5002</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1214</v>
+        <v>-2.1585</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8729</v>
+        <v>-3.577</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9943</v>
+        <v>1.4185</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2889</v>
+        <v>-3.2773</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5308</v>
+        <v>-0.982</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8196</v>
+        <v>-2.2953</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9907</v>
+        <v>-3.3095</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8066</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.184</v>
+        <v>-2.4461</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2795</v>
+        <v>0.0322</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2759</v>
+        <v>-0.1186</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0037</v>
+        <v>0.1507</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1726</v>
+        <v>-1.4921</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1142</v>
+        <v>-0.7703</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2869</v>
+        <v>-0.7218</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8919</v>
+        <v>3.0748</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8919</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0307</v>
+        <v>-2.2251</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8443</v>
+        <v>0.6684</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8136</v>
+        <v>-2.8935</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2773</v>
+        <v>-0.2889</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.982</v>
+        <v>0.5308</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2953</v>
+        <v>-0.8196</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3095</v>
+        <v>0.9907</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8633999999999999</v>
+        <v>0.8066</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4461</v>
+        <v>0.184</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0322</v>
+        <v>-1.2795</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1186</v>
+        <v>-0.2759</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1507</v>
+        <v>-1.0037</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3643</v>
+        <v>-0.2763</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0376</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3267</v>
+        <v>-0.186</v>
       </c>
       <c r="V11" t="n">
-        <v>3.0748</v>
+        <v>-1.8919</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2525</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.934699999999999</v>
+        <v>8.055</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7814</v>
+        <v>7.901599999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1531999999999994</v>
+        <v>0.1530999999999998</v>
       </c>
       <c r="G12" t="n">
         <v>12.4236</v>
@@ -1369,7 +1369,7 @@
         <v>10.1051</v>
       </c>
       <c r="L12" t="n">
-        <v>5.0182</v>
+        <v>5.018200000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-2.6998</v>
@@ -1378,7 +1378,7 @@
         <v>-1.8645</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8354999999999999</v>
+        <v>-0.8355</v>
       </c>
       <c r="P12" t="n">
         <v>-1.1598</v>
@@ -1390,13 +1390,13 @@
         <v>11.5978</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.6229</v>
+        <v>-4.5028</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.909800000000001</v>
+        <v>-2.7895</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7134</v>
+        <v>-1.7133</v>
       </c>
       <c r="V12" t="n">
         <v>1.2936</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3094</v>
+        <v>2.6867</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1173</v>
+        <v>5.7634</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8079</v>
+        <v>-3.0768</v>
       </c>
       <c r="G13" t="n">
         <v>0.8516</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3855</v>
+        <v>0.7628</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6097</v>
+        <v>0.2559</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7758</v>
+        <v>0.507</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1748</v>
+        <v>1.1469</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3758</v>
+        <v>-0.4938</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5506</v>
+        <v>1.6407</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0981</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4532</v>
+        <v>1.4253</v>
       </c>
       <c r="T14" t="n">
-        <v>0.543</v>
+        <v>0.425</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9102</v>
+        <v>1.0003</v>
       </c>
       <c r="V14" t="n">
         <v>1.3558</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4723</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4528</v>
+        <v>1.6185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0195</v>
+        <v>-1.5199</v>
       </c>
       <c r="G15" t="n">
-        <v>0.82</v>
+        <v>-2.266</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0805</v>
+        <v>-1.3793</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7395</v>
+        <v>-0.8867</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4129</v>
+        <v>0.3044</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3025</v>
+        <v>-0.0736</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1104</v>
+        <v>0.378</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4071</v>
+        <v>-2.5704</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.222</v>
+        <v>-1.3057</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6291</v>
+        <v>-1.2647</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6548</v>
+        <v>1.4547</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0578</v>
+        <v>0.7237</v>
       </c>
       <c r="U15" t="n">
-        <v>0.597</v>
+        <v>0.731</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0026</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2324</v>
+        <v>-0.3175</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7364</v>
+        <v>2.4329</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9689</v>
+        <v>-2.7504</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.266</v>
+        <v>0.1125</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3793</v>
+        <v>-1.4633</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8867</v>
+        <v>1.5758</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3044</v>
+        <v>2.4937</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0736</v>
+        <v>0.1785</v>
       </c>
       <c r="L16" t="n">
-        <v>0.378</v>
+        <v>2.3152</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5704</v>
+        <v>-2.3812</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3057</v>
+        <v>-1.6418</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2647</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1237</v>
+        <v>1.552</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8417</v>
+        <v>0.4211</v>
       </c>
       <c r="U16" t="n">
-        <v>0.282</v>
+        <v>1.131</v>
       </c>
       <c r="V16" t="n">
+        <v>-1.7501</v>
+      </c>
+      <c r="W16" t="n">
         <v>0.6778999999999999</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.7501</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.5722</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1249</v>
+        <v>-0.4909</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1436</v>
+        <v>-0.0813</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0192</v>
+        <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1921</v>
+        <v>0.0805</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2113</v>
+        <v>0.7395</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3756</v>
+        <v>0.4129</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5714</v>
+        <v>0.3025</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.947</v>
+        <v>0.1104</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6435</v>
+        <v>0.4071</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3792</v>
+        <v>-0.222</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2643</v>
+        <v>0.6291</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4261</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5895</v>
+        <v>0.1142</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1634</v>
+        <v>0.4962</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0537</v>
+        <v>-0.8127</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8431</v>
+        <v>-1.889</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8969</v>
+        <v>1.0763</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1125</v>
+        <v>-1.0192</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4633</v>
+        <v>0.1921</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5758</v>
+        <v>-1.2113</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4937</v>
+        <v>-0.3756</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1785</v>
+        <v>0.5714</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3152</v>
+        <v>-0.947</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3812</v>
+        <v>-0.6435</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6418</v>
+        <v>-0.3792</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8158</v>
+        <v>-0.2574</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1687</v>
+        <v>-0.3536</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9845</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.743</v>
+        <v>-1.8616</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7775</v>
+        <v>-3.1877</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0345</v>
+        <v>1.3262</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7663</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8891</v>
+        <v>-0.0077</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.187</v>
+        <v>-0.5972</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2978</v>
+        <v>0.5895</v>
       </c>
       <c r="V19" t="n">
         <v>1.6083</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.902</v>
+        <v>-2.8225</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0768</v>
+        <v>-0.4761</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1747</v>
+        <v>-2.3464</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2449</v>
+        <v>-3.8135</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3516</v>
+        <v>-3.8401</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5966</v>
+        <v>0.0266</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1999</v>
+        <v>-0.9285</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6574</v>
+        <v>-1.9053</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8572</v>
+        <v>0.9768</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0451</v>
+        <v>-2.8849</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3057</v>
+        <v>-1.9348</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7578</v>
+        <v>0.9034</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6256</v>
+        <v>0.4525</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1322</v>
+        <v>0.4509</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1829</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.1829</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9785</v>
+        <v>-2.9078</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9479</v>
+        <v>-3.4306</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0306</v>
+        <v>0.5229</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8135</v>
+        <v>-2.2449</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.8401</v>
+        <v>0.3516</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0266</v>
+        <v>-2.5966</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9285</v>
+        <v>-0.1999</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9053</v>
+        <v>1.6574</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9768</v>
+        <v>-1.8572</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8849</v>
+        <v>-2.0451</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9348</v>
+        <v>-1.3057</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2526</v>
+        <v>0.7521</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0193</v>
+        <v>0.2717</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2333</v>
+        <v>0.4804</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-1.1829</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9345</v>
+        <v>-5.3621</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1533</v>
+        <v>-0.1533000000000007</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.7814</v>
+        <v>-5.208699999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-12.4239</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.2409</v>
+        <v>-8.240900000000002</v>
       </c>
       <c r="I22" t="n">
         <v>-4.1831</v>
@@ -2149,7 +2149,7 @@
         <v>1.8644</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8354</v>
+        <v>0.8354000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-15.1235</v>
@@ -2170,22 +2170,22 @@
         <v>12.7576</v>
       </c>
       <c r="S22" t="n">
-        <v>5.623</v>
+        <v>7.195600000000001</v>
       </c>
       <c r="T22" t="n">
         <v>1.7133</v>
       </c>
       <c r="U22" t="n">
-        <v>3.9096</v>
+        <v>5.482500000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2936</v>
       </c>
       <c r="W22" t="n">
-        <v>7.0315</v>
+        <v>7.031500000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-8.325100000000001</v>
+        <v>-8.325099999999999</v>
       </c>
     </row>
   </sheetData>
